--- a/dataset_t6_grouped/results2/G2/G2_T1656_W0034F0003T0006Z000C1N13_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1656_W0034F0003T0006Z000C1N13_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>8.870828597149199</v>
+        <v>1.441509647036745</v>
       </c>
       <c r="D2" t="n">
-        <v>9.098896171138273</v>
+        <v>1.47857062780997</v>
       </c>
       <c r="E2" t="n">
-        <v>17.52544385617897</v>
+        <v>2.847884626629083</v>
       </c>
       <c r="F2" t="n">
-        <v>16.77108559359418</v>
+        <v>2.725301408959055</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>15.68747302500991</v>
+        <v>2.549214366564111</v>
       </c>
       <c r="D3" t="n">
-        <v>15.51446624162961</v>
+        <v>2.521100764264812</v>
       </c>
       <c r="E3" t="n">
-        <v>17.52544385617897</v>
+        <v>2.847884626629083</v>
       </c>
       <c r="F3" t="n">
-        <v>16.77108559359418</v>
+        <v>2.725301408959055</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>50.88524926640979</v>
+        <v>8.268853005791591</v>
       </c>
       <c r="D4" t="n">
-        <v>49.66357352614622</v>
+        <v>8.070330697998761</v>
       </c>
       <c r="E4" t="n">
-        <v>17.52544385617897</v>
+        <v>2.847884626629083</v>
       </c>
       <c r="F4" t="n">
-        <v>16.77108559359418</v>
+        <v>2.725301408959055</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>8.346626127776638</v>
+        <v>1.356326745763704</v>
       </c>
       <c r="D5" t="n">
-        <v>9.521340636323636</v>
+        <v>1.547217853402591</v>
       </c>
       <c r="E5" t="n">
-        <v>17.52544385617897</v>
+        <v>2.847884626629083</v>
       </c>
       <c r="F5" t="n">
-        <v>16.77108559359418</v>
+        <v>2.725301408959055</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
